--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4337" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3575" uniqueCount="380">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -270,6 +270,10 @@
     <t>*</t>
   </si>
   <si>
+    <t xml:space="preserve">fr-document-attache-components:Un component porte le type de document attaché (observation) et un component porte le document attaché (observationMedia). {component.where(observation.exists()).count() = 1 and component.where(observationMedia.exists()).count() = 1 and component.all(observation.exists() xor observationMedia.exists())}
+</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -736,82 +740,39 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Organizer.component:frTypeDocumentAttache</t>
-  </si>
-  <si>
-    <t>frTypeDocumentAttache</t>
-  </si>
-  <si>
-    <t>Type de document attaché</t>
-  </si>
-  <si>
-    <t>Organizer.component:frTypeDocumentAttache.nullFlavor</t>
+    <t>Type de document attaché (observation) et document attaché (observationMedia)</t>
   </si>
   <si>
     <t>Organizer.component.nullFlavor</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.realmCode</t>
-  </si>
-  <si>
     <t>Organizer.component.realmCode</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.typeId</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.typeId.nullFlavor</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.nullFlavor</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.assigningAuthorityName</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.typeId.displayable</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.displayable</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.typeId.root</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.root</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.typeId.extension</t>
-  </si>
-  <si>
     <t>Organizer.component.typeId.extension</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.templateId</t>
-  </si>
-  <si>
     <t>Organizer.component.templateId</t>
   </si>
   <si>
     <t>When valued in an instance, this attribute signals the imposition of a set of template-defined constraints. The value of this attribute provides a unique identifier for the templates in question</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.typeCode</t>
-  </si>
-  <si>
     <t>Organizer.component.typeCode</t>
   </si>
   <si>
@@ -824,9 +785,6 @@
     <t>OrganizerComponent.typeCode</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.contextConductionInd</t>
-  </si>
-  <si>
     <t>Organizer.component.contextConductionInd</t>
   </si>
   <si>
@@ -834,9 +792,6 @@
   </si>
   <si>
     <t>OrganizerComponent.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Organizer.component:frTypeDocumentAttache.sequenceNumber</t>
   </si>
   <si>
     <t>Organizer.component.sequenceNumber</t>
@@ -849,16 +804,10 @@
     <t>OrganizerComponent.sequenceNumber</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.sdtcPriorityNumber</t>
-  </si>
-  <si>
     <t>Organizer.component.sdtcPriorityNumber</t>
   </si>
   <si>
     <t>OrganizerComponent.sdtcPriorityNumber</t>
-  </si>
-  <si>
-    <t>Organizer.component:frTypeDocumentAttache.seperatableInd</t>
   </si>
   <si>
     <t>Organizer.component.seperatableInd</t>
@@ -871,9 +820,6 @@
     <t>OrganizerComponent.seperatableInd</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.act</t>
-  </si>
-  <si>
     <t>Organizer.component.act</t>
   </si>
   <si>
@@ -884,9 +830,6 @@
     <t>OrganizerComponent.act</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.encounter</t>
-  </si>
-  <si>
     <t>Organizer.component.encounter</t>
   </si>
   <si>
@@ -897,9 +840,6 @@
     <t>OrganizerComponent.encounter</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.observation</t>
-  </si>
-  <si>
     <t>Organizer.component.observation</t>
   </si>
   <si>
@@ -907,10 +847,10 @@
 </t>
   </si>
   <si>
+    <t>Type de document attaché</t>
+  </si>
+  <si>
     <t>OrganizerComponent.observation</t>
-  </si>
-  <si>
-    <t>Organizer.component:frTypeDocumentAttache.observationMedia</t>
   </si>
   <si>
     <t>Organizer.component.observationMedia</t>
@@ -923,7 +863,291 @@
     <t>OrganizerComponent.observationMedia</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.organizer</t>
+    <t>Organizer.component.observationMedia.nullFlavor</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.realmCode</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.typeId</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.typeId.displayable</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.typeId.root</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.typeId.extension</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.templateId</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id {http://hl7.org/cda/stds/core/StructureDefinition/xs-ID|2.0.3-sd}
+</t>
+  </si>
+  <si>
+    <t>ObservationMedia.ID</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.classCode</t>
+  </si>
+  <si>
+    <t>OBS</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAActClassObservation|2.0.3-sd</t>
+  </si>
+  <si>
+    <t>ObservationMedia.classCode</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.moodCode</t>
+  </si>
+  <si>
+    <t>ObservationMedia.moodCode</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.id</t>
+  </si>
+  <si>
+    <t>Identifiant de l'observationMedia</t>
+  </si>
+  <si>
+    <t>ObservationMedia.id</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.languageCode</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
+  </si>
+  <si>
+    <t>ObservationMedia.languageCode</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.value</t>
+  </si>
+  <si>
+    <t>Document encodé en Base 64. Le charset utilisé par défaut est iso-8859-1</t>
+  </si>
+  <si>
+    <t>ObservationMedia.value</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.value.nullFlavor</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.value.compression</t>
+  </si>
+  <si>
+    <t>Compression</t>
+  </si>
+  <si>
+    <t>Indicates whether the raw byte data is compressed, and what compression algorithm was used.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDACompressionAlgorithm|2.0.3-sd</t>
+  </si>
+  <si>
+    <t>ED.compression</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.value.integrityCheck</t>
+  </si>
+  <si>
+    <t>Integrity Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary {http://hl7.org/cda/stds/core/StructureDefinition/bin|2.0.3-sd}
+</t>
+  </si>
+  <si>
+    <t>The integrity check is a short binary value representing a cryptographically strong checksum that is calculated over the binary data. The purpose of this property, when communicated with a reference is for anyone to validate later whether the reference still resolved to the same data that the reference resolved to when the encapsulated data value with reference was created.</t>
+  </si>
+  <si>
+    <t>ED.integrityCheck</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.value.integrityCheckAlgorithm</t>
+  </si>
+  <si>
+    <t>Integrity Check Algorithm</t>
+  </si>
+  <si>
+    <t>Specifies the algorithm used to compute the integrityCheck value. The cryptographically strong checksum algorithm Secure Hash Algorithm-1 (SHA-1) is currently the industry standard. It has superseded the MD5 algorithm only a couple of years ago, when certain flaws in the security of MD5 were discovered. Currently the SHA-1 hash algorithm is the default choice for the integrity check algorithm. Note that SHA-256 is also entering widespread usage.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-IntegrityCheckAlgorithm|2.0.0</t>
+  </si>
+  <si>
+    <t>ED.integrityCheckAlgorithm</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.value.language</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>For character based information the language property specifies the human language of the text.</t>
+  </si>
+  <si>
+    <t>ED.language</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.value.mediaType</t>
+  </si>
+  <si>
+    <t>Media Type</t>
+  </si>
+  <si>
+    <t>Type MIME du document attaché</t>
+  </si>
+  <si>
+    <t>Identifies the type of the encapsulated data and identifies a method to interpret or render the data.</t>
+  </si>
+  <si>
+    <t>Valeurs les plus utilisées : 'image/gif', 'image/jpeg', 'image/png', 'image/bmp', 'image/tiff', 'text/rtf', 'text/plain', 'application/pdf' ou 'application/xml'. D'autres valeurs peuvent être utilisées.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-MediaType|3.0.0</t>
+  </si>
+  <si>
+    <t>ED.mediaType</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.value.representation</t>
+  </si>
+  <si>
+    <t>B64</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/BinaryDataEncoding|2.0.3-sd</t>
+  </si>
+  <si>
+    <t>ED.representation</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.value.xmlText</t>
+  </si>
+  <si>
+    <t>Allows for mixed text content. If @representation='B64', this SHALL be a base64binary string.</t>
+  </si>
+  <si>
+    <t>Data that is primarily intended for human interpretation or for further machine processing is outside the scope of HL7. This includes unformatted or formatted written language, multimedia data, or structured information as defined by a different standard (e.g., XML-signatures.)</t>
+  </si>
+  <si>
+    <t>This element is represented in XML as textual content. The actual name "xmlText" will not appear in a CDA instance.</t>
+  </si>
+  <si>
+    <t>ED.xmlText</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.value.reference</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/TEL
+</t>
+  </si>
+  <si>
+    <t>A telecommunication address (TEL), such as a URL for HTTP or FTP, which will resolve to precisely the same binary data that could as well have been provided as inline data.</t>
+  </si>
+  <si>
+    <t>ED.reference</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.value.thumbnail</t>
+  </si>
+  <si>
+    <t>Thumbnail</t>
+  </si>
+  <si>
+    <t>An abbreviated rendition of the full data. A thumbnail requires significantly fewer resources than the full data, while still maintaining some distinctive similarity with the full data. A thumbnail is typically used with by-reference encapsulated data. It allows a user to select data more efficiently before actually downloading through the reference.</t>
+  </si>
+  <si>
+    <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.subject</t>
+  </si>
+  <si>
+    <t>ObservationMedia.subject</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.specimen</t>
+  </si>
+  <si>
+    <t>ObservationMedia.specimen</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.performer</t>
+  </si>
+  <si>
+    <t>ObservationMedia.performer</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.author</t>
+  </si>
+  <si>
+    <t>ObservationMedia.author</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.informant</t>
+  </si>
+  <si>
+    <t>ObservationMedia.informant</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.participant</t>
+  </si>
+  <si>
+    <t>ObservationMedia.participant</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.entryRelationship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/EntryRelationship
+</t>
+  </si>
+  <si>
+    <t>ObservationMedia.entryRelationship</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.reference</t>
+  </si>
+  <si>
+    <t>ObservationMedia.reference</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.precondition</t>
+  </si>
+  <si>
+    <t>ObservationMedia.precondition</t>
+  </si>
+  <si>
+    <t>Organizer.component.observationMedia.sdtcPrecondition2</t>
+  </si>
+  <si>
+    <t>ObservationMedia.sdtcPrecondition2</t>
   </si>
   <si>
     <t>Organizer.component.organizer</t>
@@ -936,9 +1160,6 @@
     <t>OrganizerComponent.organizer</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.procedure</t>
-  </si>
-  <si>
     <t>Organizer.component.procedure</t>
   </si>
   <si>
@@ -949,9 +1170,6 @@
     <t>OrganizerComponent.procedure</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.regionOfInterest</t>
-  </si>
-  <si>
     <t>Organizer.component.regionOfInterest</t>
   </si>
   <si>
@@ -962,9 +1180,6 @@
     <t>OrganizerComponent.regionOfInterest</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.substanceAdministration</t>
-  </si>
-  <si>
     <t>Organizer.component.substanceAdministration</t>
   </si>
   <si>
@@ -975,9 +1190,6 @@
     <t>OrganizerComponent.substanceAdministration</t>
   </si>
   <si>
-    <t>Organizer.component:frTypeDocumentAttache.supply</t>
-  </si>
-  <si>
     <t>Organizer.component.supply</t>
   </si>
   <si>
@@ -986,474 +1198,6 @@
   </si>
   <si>
     <t>OrganizerComponent.supply</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia</t>
-  </si>
-  <si>
-    <t>frObservationMedia</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.nullFlavor</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.realmCode</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.typeId</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.typeId.root</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.typeId.extension</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.templateId</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.typeCode</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.sequenceNumber</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.sdtcPriorityNumber</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.seperatableInd</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.act</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.encounter</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Observation
-</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.nullFlavor</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.nullFlavor</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.realmCode</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.realmCode</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.typeId</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.typeId</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.typeId.root</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.typeId.root</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.typeId.extension</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.typeId.extension</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.templateId</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.templateId</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.ID</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id {http://hl7.org/cda/stds/core/StructureDefinition/xs-ID|2.0.3-sd}
-</t>
-  </si>
-  <si>
-    <t>ObservationMedia.ID</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.classCode</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.classCode</t>
-  </si>
-  <si>
-    <t>OBS</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDAActClassObservation|2.0.3-sd</t>
-  </si>
-  <si>
-    <t>ObservationMedia.classCode</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.moodCode</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.moodCode</t>
-  </si>
-  <si>
-    <t>ObservationMedia.moodCode</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.id</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.id</t>
-  </si>
-  <si>
-    <t>Identifiant de l'observationMedia</t>
-  </si>
-  <si>
-    <t>ObservationMedia.id</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.languageCode</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.languageCode</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
-  </si>
-  <si>
-    <t>ObservationMedia.languageCode</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.value</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.value</t>
-  </si>
-  <si>
-    <t>Document encodé en Base 64.  Le charset utilisé par défaut est iso-8859-1</t>
-  </si>
-  <si>
-    <t>ObservationMedia.value</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.value.nullFlavor</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.value.nullFlavor</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.value.compression</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.value.compression</t>
-  </si>
-  <si>
-    <t>Compression</t>
-  </si>
-  <si>
-    <t>Indicates whether the raw byte data is compressed, and what compression algorithm was used.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDACompressionAlgorithm|2.0.3-sd</t>
-  </si>
-  <si>
-    <t>ED.compression</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.value.integrityCheck</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.value.integrityCheck</t>
-  </si>
-  <si>
-    <t>Integrity Check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">base64Binary {http://hl7.org/cda/stds/core/StructureDefinition/bin|2.0.3-sd}
-</t>
-  </si>
-  <si>
-    <t>The integrity check is a short binary value representing a cryptographically strong checksum that is calculated over the binary data. The purpose of this property, when communicated with a reference is for anyone to validate later whether the reference still resolved to the same data that the reference resolved to when the encapsulated data value with reference was created.</t>
-  </si>
-  <si>
-    <t>ED.integrityCheck</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.value.integrityCheckAlgorithm</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.value.integrityCheckAlgorithm</t>
-  </si>
-  <si>
-    <t>Integrity Check Algorithm</t>
-  </si>
-  <si>
-    <t>Specifies the algorithm used to compute the integrityCheck value. The cryptographically strong checksum algorithm Secure Hash Algorithm-1 (SHA-1) is currently the industry standard. It has superseded the MD5 algorithm only a couple of years ago, when certain flaws in the security of MD5 were discovered. Currently the SHA-1 hash algorithm is the default choice for the integrity check algorithm. Note that SHA-256 is also entering widespread usage.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-IntegrityCheckAlgorithm|2.0.0</t>
-  </si>
-  <si>
-    <t>ED.integrityCheckAlgorithm</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.value.language</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.value.language</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>For character based information the language property specifies the human language of the text.</t>
-  </si>
-  <si>
-    <t>ED.language</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.value.mediaType</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.value.mediaType</t>
-  </si>
-  <si>
-    <t>Media Type</t>
-  </si>
-  <si>
-    <t>Valeurs les plus utilisées : 'image/gif' ou 'image/jpeg' ou 'image/png' ou 'image/bm'ou 'image/tiff' ou 'text/rtf' ou 'text/plain' ou 'application/pdf'ou ou 'application/xml. D’autres valeurs peuvent être utilisées.</t>
-  </si>
-  <si>
-    <t>Identifies the type of the encapsulated data and identifies a method to interpret or render the data.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-MediaType|3.0.0</t>
-  </si>
-  <si>
-    <t>ED.mediaType</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.value.representation</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.value.representation</t>
-  </si>
-  <si>
-    <t>B64</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/BinaryDataEncoding|2.0.3-sd</t>
-  </si>
-  <si>
-    <t>ED.representation</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.value.xmlText</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.value.xmlText</t>
-  </si>
-  <si>
-    <t>Allows for mixed text content. If @representation='B64', this SHALL be a base64binary string.</t>
-  </si>
-  <si>
-    <t>Data that is primarily intended for human interpretation or for further machine processing is outside the scope of HL7. This includes unformatted or formatted written language, multimedia data, or structured information as defined by a different standard (e.g., XML-signatures.)</t>
-  </si>
-  <si>
-    <t>This element is represented in XML as textual content. The actual name "xmlText" will not appear in a CDA instance.</t>
-  </si>
-  <si>
-    <t>ED.xmlText</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.value.reference</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.value.reference</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/TEL
-</t>
-  </si>
-  <si>
-    <t>A telecommunication address (TEL), such as a URL for HTTP or FTP, which will resolve to precisely the same binary data that could as well have been provided as inline data.</t>
-  </si>
-  <si>
-    <t>ED.reference</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.value.thumbnail</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.value.thumbnail</t>
-  </si>
-  <si>
-    <t>Thumbnail</t>
-  </si>
-  <si>
-    <t>An abbreviated rendition of the full data. A thumbnail requires significantly fewer resources than the full data, while still maintaining some distinctive similarity with the full data. A thumbnail is typically used with by-reference encapsulated data. It allows a user to select data more efficiently before actually downloading through the reference.</t>
-  </si>
-  <si>
-    <t>ED.thumbnail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
-</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.subject</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.subject</t>
-  </si>
-  <si>
-    <t>ObservationMedia.subject</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.specimen</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.specimen</t>
-  </si>
-  <si>
-    <t>ObservationMedia.specimen</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.performer</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.performer</t>
-  </si>
-  <si>
-    <t>ObservationMedia.performer</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.author</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.author</t>
-  </si>
-  <si>
-    <t>ObservationMedia.author</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.informant</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.informant</t>
-  </si>
-  <si>
-    <t>ObservationMedia.informant</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.participant</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.participant</t>
-  </si>
-  <si>
-    <t>ObservationMedia.participant</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.entryRelationship</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.entryRelationship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/EntryRelationship
-</t>
-  </si>
-  <si>
-    <t>ObservationMedia.entryRelationship</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.reference</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.reference</t>
-  </si>
-  <si>
-    <t>ObservationMedia.reference</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.precondition</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.precondition</t>
-  </si>
-  <si>
-    <t>ObservationMedia.precondition</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.observationMedia.sdtcPrecondition2</t>
-  </si>
-  <si>
-    <t>Organizer.component.observationMedia.sdtcPrecondition2</t>
-  </si>
-  <si>
-    <t>ObservationMedia.sdtcPrecondition2</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.organizer</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.procedure</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.regionOfInterest</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.substanceAdministration</t>
-  </si>
-  <si>
-    <t>Organizer.component:frObservationMedia.supply</t>
   </si>
 </sst>
 </file>
@@ -1770,12 +1514,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK139"/>
+  <dimension ref="A1:AK114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="73.8828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.86328125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="57.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2021,25 +1765,25 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>81</v>
@@ -2057,11 +1801,11 @@
         <v>75</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -2088,11 +1832,11 @@
         <v>75</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>75</v>
@@ -2110,7 +1854,7 @@
         <v>75</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>81</v>
@@ -2130,10 +1874,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2156,11 +1900,11 @@
         <v>75</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2211,7 +1955,7 @@
         <v>75</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>81</v>
@@ -2231,10 +1975,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2257,11 +2001,11 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2312,7 +2056,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>81</v>
@@ -2324,7 +2068,7 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
@@ -2332,17 +2076,17 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>81</v>
@@ -2360,11 +2104,11 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -2391,11 +2135,11 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>75</v>
@@ -2413,7 +2157,7 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>81</v>
@@ -2433,17 +2177,17 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>81</v>
@@ -2461,11 +2205,11 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2516,7 +2260,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>81</v>
@@ -2536,17 +2280,17 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>81</v>
@@ -2564,11 +2308,11 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2619,7 +2363,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>81</v>
@@ -2639,17 +2383,17 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>76</v>
@@ -2667,11 +2411,11 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2680,7 +2424,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>75</v>
@@ -2722,7 +2466,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>81</v>
@@ -2742,17 +2486,17 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>76</v>
@@ -2770,11 +2514,11 @@
         <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2825,7 +2569,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -2845,10 +2589,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2871,13 +2615,13 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2928,7 +2672,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -2948,17 +2692,17 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>81</v>
@@ -2976,11 +2720,11 @@
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3007,11 +2751,11 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>75</v>
@@ -3029,7 +2773,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3049,17 +2793,17 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>81</v>
@@ -3077,11 +2821,11 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3132,7 +2876,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3152,17 +2896,17 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>81</v>
@@ -3180,11 +2924,11 @@
         <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3235,7 +2979,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3255,17 +2999,17 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>81</v>
@@ -3283,11 +3027,11 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3299,7 +3043,7 @@
         <v>75</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>75</v>
@@ -3338,7 +3082,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3358,17 +3102,17 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>81</v>
@@ -3386,11 +3130,11 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3441,7 +3185,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3461,10 +3205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3478,7 +3222,7 @@
         <v>76</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>75</v>
@@ -3487,7 +3231,7 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -3501,7 +3245,7 @@
         <v>75</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>75</v>
@@ -3516,11 +3260,11 @@
         <v>75</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>75</v>
@@ -3538,7 +3282,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3558,10 +3302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3575,7 +3319,7 @@
         <v>76</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>75</v>
@@ -3584,7 +3328,7 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -3595,7 +3339,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>75</v>
@@ -3613,11 +3357,11 @@
         <v>75</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>75</v>
@@ -3635,7 +3379,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3655,10 +3399,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3672,7 +3416,7 @@
         <v>76</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>75</v>
@@ -3681,13 +3425,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3738,7 +3482,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -3758,10 +3502,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3784,7 +3528,7 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -3837,7 +3581,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -3857,10 +3601,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3874,7 +3618,7 @@
         <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>75</v>
@@ -3883,13 +3627,13 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3916,11 +3660,11 @@
         <v>75</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>75</v>
@@ -3938,7 +3682,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -3958,17 +3702,17 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>81</v>
@@ -3986,11 +3730,11 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4017,11 +3761,11 @@
         <v>75</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>75</v>
@@ -4039,7 +3783,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4059,10 +3803,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4078,7 +3822,7 @@
         <v>76</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>75</v>
@@ -4087,11 +3831,11 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4103,7 +3847,7 @@
         <v>75</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>75</v>
@@ -4142,7 +3886,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4162,17 +3906,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>76</v>
@@ -4181,7 +3925,7 @@
         <v>76</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>75</v>
@@ -4190,11 +3934,11 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4206,7 +3950,7 @@
         <v>75</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>75</v>
@@ -4245,7 +3989,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4265,17 +4009,17 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>81</v>
@@ -4293,11 +4037,11 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4309,7 +4053,7 @@
         <v>75</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>75</v>
@@ -4348,7 +4092,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4368,17 +4112,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>81</v>
@@ -4396,11 +4140,11 @@
         <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4451,7 +4195,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4471,17 +4215,17 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>81</v>
@@ -4490,7 +4234,7 @@
         <v>76</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>75</v>
@@ -4499,11 +4243,11 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4515,7 +4259,7 @@
         <v>75</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>75</v>
@@ -4554,7 +4298,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4574,10 +4318,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4600,11 +4344,11 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4655,7 +4399,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4675,10 +4419,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4701,11 +4445,11 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4756,7 +4500,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4776,17 +4520,17 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>81</v>
@@ -4804,11 +4548,11 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4859,7 +4603,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -4879,17 +4623,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>81</v>
@@ -4907,11 +4651,11 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4962,7 +4706,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -4982,17 +4726,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>81</v>
@@ -5010,11 +4754,11 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5065,7 +4809,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5085,10 +4829,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5111,7 +4855,7 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -5164,7 +4908,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5184,10 +4928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5201,7 +4945,7 @@
         <v>76</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>75</v>
@@ -5210,13 +4954,13 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5243,11 +4987,11 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5265,7 +5009,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5285,17 +5029,17 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>81</v>
@@ -5313,11 +5057,11 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5344,11 +5088,11 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5366,7 +5110,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5386,10 +5130,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5414,11 +5158,11 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5430,7 +5174,7 @@
         <v>75</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>75</v>
@@ -5469,7 +5213,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5489,17 +5233,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>81</v>
@@ -5517,11 +5261,11 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5572,7 +5316,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5592,17 +5336,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>81</v>
@@ -5620,11 +5364,11 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5675,7 +5419,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5695,17 +5439,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>81</v>
@@ -5723,11 +5467,11 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5778,7 +5522,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5798,17 +5542,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>81</v>
@@ -5826,11 +5570,11 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5881,7 +5625,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -5901,10 +5645,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5927,11 +5671,11 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5982,7 +5726,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6002,10 +5746,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6028,11 +5772,11 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6083,7 +5827,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6103,17 +5847,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>81</v>
@@ -6131,11 +5875,11 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6186,7 +5930,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6206,17 +5950,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>81</v>
@@ -6234,11 +5978,11 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6289,7 +6033,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6309,17 +6053,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>81</v>
@@ -6337,11 +6081,11 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6392,7 +6136,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6412,10 +6156,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6429,7 +6173,7 @@
         <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>75</v>
@@ -6438,13 +6182,13 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6495,7 +6239,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6515,10 +6259,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6541,7 +6285,7 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6594,7 +6338,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6614,10 +6358,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6640,7 +6384,7 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6693,7 +6437,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -6713,10 +6457,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6739,7 +6483,7 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6792,7 +6536,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -6812,10 +6556,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6838,7 +6582,7 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6891,7 +6635,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -6911,10 +6655,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6937,7 +6681,7 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6990,7 +6734,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7010,10 +6754,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7036,7 +6780,7 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -7089,7 +6833,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -7109,10 +6853,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7135,7 +6879,7 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -7188,7 +6932,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -7208,10 +6952,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7234,7 +6978,7 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -7287,7 +7031,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -7307,10 +7051,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7333,7 +7077,7 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -7386,7 +7130,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7404,12 +7148,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7417,13 +7161,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>75</v>
@@ -7432,9 +7176,11 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="L56" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7473,17 +7219,19 @@
         <v>75</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AC56" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>232</v>
+        <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -7506,17 +7254,17 @@
         <v>233</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F57" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>76</v>
@@ -7531,12 +7279,12 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="M57" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="L57" s="2"/>
+      <c r="M57" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7562,13 +7310,11 @@
         <v>75</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>75</v>
@@ -7586,13 +7332,13 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>228</v>
+        <v>91</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>75</v>
@@ -7606,23 +7352,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E58" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>75</v>
@@ -7634,11 +7378,11 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7665,11 +7409,13 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>75</v>
@@ -7687,13 +7433,13 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>75</v>
@@ -7707,10 +7453,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7721,7 +7467,7 @@
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>75</v>
@@ -7733,11 +7479,11 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7788,19 +7534,19 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>75</v>
@@ -7808,16 +7554,18 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F60" t="s" s="2">
         <v>81</v>
       </c>
@@ -7834,11 +7582,11 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7865,13 +7613,11 @@
         <v>75</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -7889,7 +7635,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -7901,7 +7647,7 @@
         <v>75</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>75</v>
@@ -7909,17 +7655,17 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>81</v>
@@ -7937,11 +7683,11 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7968,11 +7714,13 @@
         <v>75</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>75</v>
@@ -7990,7 +7738,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -8010,17 +7758,17 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>81</v>
@@ -8038,11 +7786,11 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8093,7 +7841,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -8113,20 +7861,20 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>76</v>
@@ -8141,11 +7889,11 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8154,7 +7902,7 @@
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="S63" t="s" s="2">
         <v>75</v>
@@ -8196,7 +7944,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -8216,17 +7964,17 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>76</v>
@@ -8244,11 +7992,11 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8257,7 +8005,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>75</v>
@@ -8299,7 +8047,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -8319,23 +8067,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E65" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>75</v>
@@ -8347,11 +8093,11 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8402,13 +8148,13 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>75</v>
@@ -8422,10 +8168,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8436,7 +8182,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>75</v>
@@ -8448,16 +8194,14 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L66" s="2"/>
-      <c r="M66" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
-        <v>75</v>
+        <v>244</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
@@ -8479,13 +8223,11 @@
         <v>75</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>75</v>
+        <v>245</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>75</v>
@@ -8503,13 +8245,13 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>123</v>
+        <v>246</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>75</v>
@@ -8523,10 +8265,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8549,18 +8291,18 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
-        <v>257</v>
+        <v>75</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>75</v>
+        <v>248</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>75</v>
@@ -8578,11 +8320,13 @@
         <v>75</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>258</v>
+        <v>75</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>75</v>
@@ -8600,7 +8344,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8620,10 +8364,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8646,7 +8390,7 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>108</v>
+        <v>251</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8657,7 +8401,7 @@
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>75</v>
@@ -8699,7 +8443,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -8719,10 +8463,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8745,7 +8489,7 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8798,7 +8542,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -8818,10 +8562,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8844,7 +8588,7 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8897,7 +8641,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -8917,10 +8661,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8943,7 +8687,7 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8996,7 +8740,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -9016,10 +8760,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9042,7 +8786,7 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -9095,7 +8839,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -9115,10 +8859,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9141,9 +8885,11 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="L73" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9194,7 +8940,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -9214,10 +8960,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9240,9 +8986,11 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="L74" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9293,7 +9041,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -9313,16 +9061,18 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F75" t="s" s="2">
         <v>81</v>
       </c>
@@ -9339,10 +9089,12 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>289</v>
+        <v>87</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9368,13 +9120,11 @@
         <v>75</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>75</v>
@@ -9392,7 +9142,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>290</v>
+        <v>91</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -9412,10 +9162,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9426,7 +9176,7 @@
         <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>75</v>
@@ -9438,10 +9188,12 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>293</v>
+        <v>93</v>
       </c>
       <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
+      <c r="M76" t="s" s="2">
+        <v>94</v>
+      </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9491,13 +9243,13 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>294</v>
+        <v>95</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>75</v>
@@ -9511,10 +9263,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9537,10 +9289,12 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>297</v>
+        <v>97</v>
       </c>
       <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
+      <c r="M77" t="s" s="2">
+        <v>98</v>
+      </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9590,7 +9344,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>298</v>
+        <v>99</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -9602,7 +9356,7 @@
         <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
@@ -9610,16 +9364,18 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E78" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F78" t="s" s="2">
         <v>81</v>
       </c>
@@ -9636,10 +9392,12 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>301</v>
+        <v>87</v>
       </c>
       <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
+      <c r="M78" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -9665,13 +9423,11 @@
         <v>75</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>75</v>
@@ -9689,7 +9445,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>302</v>
+        <v>91</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -9709,16 +9465,18 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="F79" t="s" s="2">
         <v>81</v>
       </c>
@@ -9735,10 +9493,12 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>305</v>
+        <v>104</v>
       </c>
       <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
+      <c r="M79" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9788,7 +9548,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>306</v>
+        <v>106</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9808,16 +9568,18 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>308</v>
+        <v>276</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E80" s="2"/>
+      <c r="E80" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="F80" t="s" s="2">
         <v>81</v>
       </c>
@@ -9834,10 +9596,12 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>309</v>
+        <v>109</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
+      <c r="M80" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9887,7 +9651,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>310</v>
+        <v>111</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -9907,18 +9671,18 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E81" s="2"/>
+      <c r="E81" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="F81" t="s" s="2">
         <v>76</v>
       </c>
@@ -9935,12 +9699,12 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="M81" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="L81" s="2"/>
+      <c r="M81" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -9948,7 +9712,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>75</v>
@@ -9990,13 +9754,13 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>228</v>
+        <v>117</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>75</v>
@@ -10010,20 +9774,20 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>313</v>
+        <v>278</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>76</v>
@@ -10038,11 +9802,11 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10069,11 +9833,13 @@
         <v>75</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>75</v>
@@ -10091,7 +9857,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -10111,10 +9877,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>314</v>
+        <v>279</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>239</v>
+        <v>279</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10137,11 +9903,11 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>93</v>
+        <v>242</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10192,7 +9958,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -10212,10 +9978,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>315</v>
+        <v>280</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10238,12 +10004,10 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>96</v>
+        <v>281</v>
       </c>
       <c r="L84" s="2"/>
-      <c r="M84" t="s" s="2">
-        <v>97</v>
-      </c>
+      <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10293,7 +10057,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>98</v>
+        <v>282</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -10305,34 +10069,32 @@
         <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>243</v>
+        <v>283</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E85" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>75</v>
@@ -10341,20 +10103,18 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>75</v>
+        <v>284</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>75</v>
+        <v>284</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>75</v>
@@ -10372,11 +10132,11 @@
         <v>75</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>89</v>
+        <v>285</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>75</v>
@@ -10394,10 +10154,10 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>90</v>
+        <v>286</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>76</v>
@@ -10412,28 +10172,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E86" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>75</v>
@@ -10442,20 +10200,18 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="L86" s="2"/>
-      <c r="M86" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>75</v>
@@ -10473,13 +10229,11 @@
         <v>75</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>75</v>
@@ -10497,10 +10251,10 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>105</v>
+        <v>288</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -10517,18 +10271,16 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E87" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>81</v>
       </c>
@@ -10545,11 +10297,13 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L87" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="M87" t="s" s="2">
-        <v>109</v>
+        <v>290</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10600,13 +10354,13 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>110</v>
+        <v>291</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>75</v>
@@ -10620,20 +10374,18 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>319</v>
+        <v>292</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E88" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>76</v>
@@ -10648,12 +10400,10 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="L88" s="2"/>
-      <c r="M88" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -10661,7 +10411,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>75</v>
@@ -10679,13 +10429,11 @@
         <v>75</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>75</v>
+        <v>293</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>75</v>
@@ -10703,7 +10451,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>116</v>
+        <v>294</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -10721,20 +10469,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E89" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>76</v>
       </c>
@@ -10742,7 +10488,7 @@
         <v>76</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>75</v>
@@ -10751,12 +10497,12 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L89" s="2"/>
-      <c r="M89" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10806,10 +10552,10 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>120</v>
+        <v>297</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>76</v>
@@ -10826,21 +10572,23 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E90" s="2"/>
+      <c r="E90" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>75</v>
@@ -10852,11 +10600,11 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>254</v>
+        <v>88</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10883,13 +10631,11 @@
         <v>75</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>75</v>
@@ -10907,13 +10653,13 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>75</v>
@@ -10927,16 +10673,18 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E91" s="2"/>
+      <c r="E91" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="F91" t="s" s="2">
         <v>81</v>
       </c>
@@ -10953,14 +10701,16 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
+      <c r="M91" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
-        <v>257</v>
+        <v>75</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
@@ -10982,11 +10732,11 @@
         <v>75</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>75</v>
@@ -11004,7 +10754,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -11024,16 +10774,18 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>261</v>
+        <v>304</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E92" s="2"/>
+      <c r="E92" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="F92" t="s" s="2">
         <v>81</v>
       </c>
@@ -11050,10 +10802,12 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>108</v>
+        <v>306</v>
       </c>
       <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
+      <c r="M92" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11061,7 +10815,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>75</v>
@@ -11103,7 +10857,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>263</v>
+        <v>308</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -11123,16 +10877,18 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E93" s="2"/>
+      <c r="E93" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="F93" t="s" s="2">
         <v>81</v>
       </c>
@@ -11149,10 +10905,12 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>266</v>
+        <v>87</v>
       </c>
       <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
+      <c r="M93" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11178,13 +10936,11 @@
         <v>75</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>75</v>
+        <v>312</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>75</v>
@@ -11202,7 +10958,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>267</v>
+        <v>313</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -11222,16 +10978,18 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E94" s="2"/>
+      <c r="E94" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="F94" t="s" s="2">
         <v>81</v>
       </c>
@@ -11248,10 +11006,12 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>266</v>
+        <v>87</v>
       </c>
       <c r="L94" s="2"/>
-      <c r="M94" s="2"/>
+      <c r="M94" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11301,7 +11061,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>270</v>
+        <v>317</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -11319,18 +11079,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E95" s="2"/>
+      <c r="E95" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="F95" t="s" s="2">
         <v>81</v>
       </c>
@@ -11338,7 +11100,7 @@
         <v>76</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>75</v>
@@ -11347,11 +11109,17 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
-      <c r="N95" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -11376,13 +11144,11 @@
         <v>75</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>75</v>
+        <v>323</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>75</v>
@@ -11400,7 +11166,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>274</v>
+        <v>324</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -11418,12 +11184,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>276</v>
+        <v>325</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11437,7 +11203,7 @@
         <v>76</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>75</v>
@@ -11446,7 +11212,7 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>277</v>
+        <v>87</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11460,7 +11226,7 @@
         <v>75</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>75</v>
+        <v>326</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>75</v>
@@ -11475,13 +11241,11 @@
         <v>75</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>75</v>
+        <v>327</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>75</v>
@@ -11499,7 +11263,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -11519,10 +11283,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>280</v>
+        <v>329</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11545,11 +11309,17 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="L97" s="2"/>
-      <c r="M97" s="2"/>
-      <c r="N97" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>75</v>
@@ -11598,7 +11368,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>282</v>
+        <v>333</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -11618,16 +11388,18 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>284</v>
+        <v>334</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E98" s="2"/>
+      <c r="E98" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="F98" t="s" s="2">
         <v>81</v>
       </c>
@@ -11644,10 +11416,12 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="L98" s="2"/>
-      <c r="M98" s="2"/>
+      <c r="M98" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -11697,7 +11471,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -11717,18 +11491,20 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="F99" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>76</v>
@@ -11743,10 +11519,12 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>289</v>
+        <v>180</v>
       </c>
       <c r="L99" s="2"/>
-      <c r="M99" s="2"/>
+      <c r="M99" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -11796,7 +11574,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>290</v>
+        <v>342</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -11808,7 +11586,7 @@
         <v>75</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>75</v>
+        <v>343</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>75</v>
@@ -11816,18 +11594,16 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E100" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>81</v>
       </c>
@@ -11844,12 +11620,10 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>86</v>
+        <v>212</v>
       </c>
       <c r="L100" s="2"/>
-      <c r="M100" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M100" s="2"/>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -11875,11 +11649,13 @@
         <v>75</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y100" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z100" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>75</v>
@@ -11897,7 +11673,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>90</v>
+        <v>345</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -11917,10 +11693,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11943,12 +11719,10 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>92</v>
+        <v>214</v>
       </c>
       <c r="L101" s="2"/>
-      <c r="M101" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M101" s="2"/>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -11998,7 +11772,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>94</v>
+        <v>347</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -12018,10 +11792,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12032,7 +11806,7 @@
         <v>81</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>75</v>
@@ -12044,12 +11818,10 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>96</v>
+        <v>216</v>
       </c>
       <c r="L102" s="2"/>
-      <c r="M102" t="s" s="2">
-        <v>97</v>
-      </c>
+      <c r="M102" s="2"/>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12099,19 +11871,19 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>98</v>
+        <v>349</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
@@ -12119,23 +11891,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E103" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>75</v>
@@ -12147,12 +11917,10 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>86</v>
+        <v>218</v>
       </c>
       <c r="L103" s="2"/>
-      <c r="M103" t="s" s="2">
-        <v>87</v>
-      </c>
+      <c r="M103" s="2"/>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -12178,11 +11946,13 @@
         <v>75</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y103" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z103" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>75</v>
@@ -12200,13 +11970,13 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>90</v>
+        <v>351</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>75</v>
@@ -12220,23 +11990,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E104" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>75</v>
@@ -12248,12 +12016,10 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="L104" s="2"/>
-      <c r="M104" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="M104" s="2"/>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -12303,13 +12069,13 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>105</v>
+        <v>353</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>75</v>
@@ -12323,23 +12089,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E105" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>75</v>
@@ -12351,12 +12115,10 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>108</v>
+        <v>222</v>
       </c>
       <c r="L105" s="2"/>
-      <c r="M105" t="s" s="2">
-        <v>109</v>
-      </c>
+      <c r="M105" s="2"/>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -12406,13 +12168,13 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>110</v>
+        <v>355</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>75</v>
@@ -12426,23 +12188,21 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E106" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>75</v>
@@ -12454,12 +12214,10 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>113</v>
+        <v>357</v>
       </c>
       <c r="L106" s="2"/>
-      <c r="M106" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="M106" s="2"/>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -12467,7 +12225,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>75</v>
@@ -12509,13 +12267,13 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>116</v>
+        <v>358</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>75</v>
@@ -12529,23 +12287,21 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E107" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>75</v>
@@ -12557,12 +12313,10 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>103</v>
+        <v>224</v>
       </c>
       <c r="L107" s="2"/>
-      <c r="M107" t="s" s="2">
-        <v>119</v>
-      </c>
+      <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -12612,13 +12366,13 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>75</v>
@@ -12632,10 +12386,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12658,12 +12412,10 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>96</v>
+        <v>226</v>
       </c>
       <c r="L108" s="2"/>
-      <c r="M108" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -12713,7 +12465,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>123</v>
+        <v>362</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -12733,10 +12485,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12747,7 +12499,7 @@
         <v>81</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>75</v>
@@ -12759,7 +12511,7 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>352</v>
+        <v>228</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12812,13 +12564,13 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>75</v>
@@ -12830,12 +12582,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12843,13 +12595,13 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>75</v>
@@ -12858,18 +12610,18 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>86</v>
+        <v>366</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
-        <v>356</v>
+        <v>75</v>
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>356</v>
+        <v>75</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>75</v>
@@ -12887,11 +12639,13 @@
         <v>75</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y110" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z110" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>75</v>
@@ -12909,10 +12663,10 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>76</v>
@@ -12927,12 +12681,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12940,13 +12694,13 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>75</v>
@@ -12955,18 +12709,18 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>86</v>
+        <v>369</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="S111" t="s" s="2">
         <v>75</v>
@@ -12984,11 +12738,13 @@
         <v>75</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -13006,10 +12762,10 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>76</v>
@@ -13026,10 +12782,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13052,14 +12808,10 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="L112" s="2"/>
+      <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -13109,13 +12861,13 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>75</v>
@@ -13129,10 +12881,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13155,7 +12907,7 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>92</v>
+        <v>375</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13184,11 +12936,13 @@
         <v>75</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y113" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z113" t="s" s="2">
-        <v>368</v>
+        <v>75</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>75</v>
@@ -13206,7 +12960,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13224,12 +12978,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13237,13 +12991,13 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>75</v>
@@ -13252,11 +13006,9 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="L114" s="2"/>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13307,10 +13059,10 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>76</v>
@@ -13325,2515 +13077,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L115" s="2"/>
-      <c r="M115" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y115" s="2"/>
-      <c r="Z115" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E116" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="F116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L116" s="2"/>
-      <c r="M116" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y116" s="2"/>
-      <c r="Z116" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E117" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="F117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="L117" s="2"/>
-      <c r="M117" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E118" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="F118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L118" s="2"/>
-      <c r="M118" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y118" s="2"/>
-      <c r="Z118" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E119" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="F119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L119" s="2"/>
-      <c r="M119" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E120" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="F120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y120" s="2"/>
-      <c r="Z120" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="M121" s="2"/>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y121" s="2"/>
-      <c r="Z121" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E123" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="F123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="L123" s="2"/>
-      <c r="M123" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E124" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="F124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="L124" s="2"/>
-      <c r="M124" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="L125" s="2"/>
-      <c r="M125" s="2"/>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="L126" s="2"/>
-      <c r="M126" s="2"/>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="L127" s="2"/>
-      <c r="M127" s="2"/>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="L128" s="2"/>
-      <c r="M128" s="2"/>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-      <c r="P128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="L129" s="2"/>
-      <c r="M129" s="2"/>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="130" hidden="true">
-      <c r="A130" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="L130" s="2"/>
-      <c r="M130" s="2"/>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
-      <c r="P130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="L131" s="2"/>
-      <c r="M131" s="2"/>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="L132" s="2"/>
-      <c r="M132" s="2"/>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
-      <c r="P132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="L133" s="2"/>
-      <c r="M133" s="2"/>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="L134" s="2"/>
-      <c r="M134" s="2"/>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="L135" s="2"/>
-      <c r="M135" s="2"/>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="L136" s="2"/>
-      <c r="M136" s="2"/>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
-      <c r="P136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="L137" s="2"/>
-      <c r="M137" s="2"/>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
-      <c r="P137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="138" hidden="true">
-      <c r="A138" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="L138" s="2"/>
-      <c r="M138" s="2"/>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
-      <c r="P138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="139" hidden="true">
-      <c r="A139" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="L139" s="2"/>
-      <c r="M139" s="2"/>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
-      <c r="P139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK139">
+  <autoFilter ref="A1:AK114">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15843,7 +13088,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI138">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
